--- a/outputs/evaluation/decision/v1/CF_M08/run_3/CF_M08_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_3/CF_M08_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>Funciona como un proxy inverso y balanceador de carga. • Gestiona el enrutamiento de solicitudes HTTP y HTTPS hacia la aplicación Next.js (System Service). • Expone los puertos 80 (HTTP) y 443 (HTTPS) al mundo exterior y redirige el tráfico a los servicios internos según las reglas definidas.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R_28, C_07</t>
+          <t>R_22, R_23, C_04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_01, AU_02, AU_05, AU_16, AU_23, AU_24, P_01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -496,226 +496,277 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The system must be scalable to handle an increase in the number of users and volume of data.; 12g. Expansion or Growth Requirements</t>
+          <t>The system must have an uptime of 99.9% and be able to recover from failures in less than 1 hour.; Uptime monitoring that demonstrates 99.9% uptime and disaster recovery tests that meet the specified recovery time.; 12e. Robustness or Fault Tolerance Requirements</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>User; Security Service; Traefik; AU_16; HTTP; HTTPS; Microservices</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
+directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6187</v>
+        <v>0.7491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components, promoting modularity, code reuse, and maintainability.</t>
+          <t>Interactúa con varios servicios externos para funcionalidades específicas: ◦ Autenticación: Utiliza Google para la autenticación de usuarios. ◦ Almacenamiento en la nube: Utiliza Amazon S3 para almacenar y recuperar archivos. ◦ Procesamiento de pagos: Integra con Stripe para manejar pagos y suscripciones. ◦ Análisis: Implementa Google Analytics para rastrear y analizar el tráfico del sitio. ◦ Monitoreo de errores: Utiliza Sentry para rastrear y gestionar errores en la aplicación. ◦ Correo Electrónico: Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>R_04, R_07, R_09, R_14, R_20, R_21, R_22, R_23, C_03, C_04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_03, AU_19, AU_21, AU_22, AU_18, AU_20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14a. Maintenance Requirements</t>
+          <t>The system must be able to authenticate existing users through email.; The system must be able to save all images of all products/users in the system.; A company must have access to the system dashboard in order to use the various internal functionalities and additional information (statistics, values, etc.).; Every route must have an associated budget (which can be 0) which the user must be able to pay through the use of the system when returning the product.; The system must protect user information through secure authentication.; The system must pass security audits without critical vulnerabilities.; The system must have an uptime of 99.9% and be able to recover from failures in less than 1 hour.; Uptime monitoring that demonstrates 99.9% uptime and disaster recovery tests that meet the specified recovery time.; 15c. Privacy Requirements; 12e. Robustness or Fault Tolerance Requirements</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Component-Based</t>
+          <t>System Service; AU_19; AU_21; AU_22; AU_18; AU_20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.7297</v>
+        <v>0.6754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects, allowing them to react appropriately to state changes.</t>
+          <t>Proporciona la base de datos relacional para almacenar los datos de la aplicación. • Se comunica directamente con Prisma para gestionar las consultas de la base de datos.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>R_28, R_29, C_07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_04, AU_07, AU_17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14a. Maintenance Requirements</t>
+          <t>The system must be scalable to handle an increase in the number of users and volume of data.; Ability to increase server resources and maintain performance with a 50% increase in workload.; 12g. Expansion or Growth Requirements</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Observer Pattern</t>
+          <t>Data Service; PostgreSQL; AU_17</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.6169</v>
+        <v>0.7517</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance, used to manage shared resources like database connections.</t>
+          <t>Cabe destacar que cada uno de estos servicios esta contenido en un contenedor de Docker.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>R_22, R_23, C_04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_09, P_01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14a. Maintenance Requirements</t>
+          <t>The system must have an uptime of 99.9% and be able to recover from failures in less than 1 hour.; Uptime monitoring that demonstrates 99.9% uptime and disaster recovery tests that meet the specified recovery time.; 12e. Robustness or Fault Tolerance Requirements</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Singleton Pattern</t>
+          <t>Docker; Microservices</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>It is designed to simplify access and database management</t>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.671</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables. Cada componente encapsula su propia lógica, estilos y estructura, lo que permite que estos se desarrollen, mantengan y prueben de manera aislada.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R_18, R_24, R_25, C_02, C_05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>The user interface must be intuitive and easy to use for non-technical users.; The system must be easy to maintain and update with clear and complete documentation.; Complete and updated documentation, and average time for implementing updates and problem resolution not exceeding 2 hours.; 11a. Ease of Use Requirements; 14a. Maintenance Requirements</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Component-Based</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7347</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>AD_08</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Docker is a containerization platform used to manage the execution of the application services, allowing to create an application and package it together with its dependencies and libraries.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C_05, C_06</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>14a. Maintenance Requirements; 14c. Adaptability Requirements</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Docker</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>El patrón Observer establece una relación de uno a muchos entre objetos, donde un objeto conocido como el sujeto mantiene una lista de otros objetos llamados observadores. Estos observadores se suscriben al sujeto para recibir notificaciones de cambios en su estado. Cuando el estado del sujeto cambia, notifica automáticamente a todos sus observadores, permitiendo que estos reaccionen adecuadamente.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>R_24, R_25, C_05</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>The system must be easy to maintain and update with clear and complete documentation.; Complete and updated documentation, and average time for implementing updates and problem resolution not exceeding 2 hours.; 14a. Maintenance Requirements</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Observer Pattern</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>CF_M08_AD07</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>0.6291</v>
+      <c r="J7" t="n">
+        <v>0.6056</v>
       </c>
     </row>
   </sheetData>
